--- a/docs/创作目录/标题库导出_20260427-7.xlsx
+++ b/docs/创作目录/标题库导出_20260427-7.xlsx
@@ -1,362 +1,189 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="31140" windowHeight="12760" activeTab="5"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="31140" windowHeight="12760" tabRatio="600" firstSheet="0" activeTab="5" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="公众号-教育培训" sheetId="1" r:id="rId1"/>
-    <sheet name="公众号-情感故事" sheetId="2" r:id="rId2"/>
-    <sheet name="公众号-职场成长" sheetId="3" r:id="rId3"/>
-    <sheet name="未分类-历史文化" sheetId="4" r:id="rId4"/>
-    <sheet name="公众号-健康养生" sheetId="5" r:id="rId5"/>
-    <sheet name="生成规则" sheetId="6" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="公众号-教育培训" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="公众号-情感故事" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="公众号-职场成长" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="未分类-历史文化" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="公众号-健康养生" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="生成规则" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="48">
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>标题名称</t>
-  </si>
-  <si>
-    <t>用户名</t>
-  </si>
-  <si>
-    <t>样式风格</t>
-  </si>
-  <si>
-    <t>描述</t>
-  </si>
-  <si>
-    <t>推荐日期</t>
-  </si>
-  <si>
-    <t>是否创作完成</t>
-  </si>
-  <si>
-    <t>f3fbece663d44fa1bcfc335e8741b56f</t>
-  </si>
-  <si>
-    <t>别再瞎发了！公众号文章怎么发，才能进入流量池？我的方法很简单</t>
-  </si>
-  <si>
-    <t>taotao</t>
-  </si>
-  <si>
-    <t>基础风格</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>2026-04-28</t>
-  </si>
-  <si>
-    <t>0aa7a8cbf24e4160ae6ffd55fd6d592c</t>
-  </si>
-  <si>
-    <t>50岁恋综：中年人的情感困境</t>
-  </si>
-  <si>
-    <t>yanghm</t>
-  </si>
-  <si>
-    <t>41c3ce003ab04d209ec5a3e44f29d7f5</t>
-  </si>
-  <si>
-    <t>这个星座别在亲密关系中回避情感依赖</t>
-  </si>
-  <si>
-    <t>shuxing</t>
-  </si>
-  <si>
-    <t>科技蓝标签风</t>
-  </si>
-  <si>
-    <t>85f138d247c2405b8917649a16e0cf93</t>
-  </si>
-  <si>
-    <t>心理学上有个词叫：情感饥饿（我坚持不找你，不是因为不想你，更不是因为不爱你，而是因为你给我的感觉，像是我在打扰你）</t>
-  </si>
-  <si>
-    <t>sumy</t>
-  </si>
-  <si>
-    <t>法式奶油日落风</t>
-  </si>
-  <si>
-    <t>650c156ce3a0424b874c64efe84944b8</t>
-  </si>
-  <si>
-    <t>心理学上说：越是分房睡、经济AA制、不干涉对方隐私的夫妻，感情浓度往往越低，越把婚姻过成</t>
-  </si>
-  <si>
-    <t>fangwj</t>
-  </si>
-  <si>
-    <t>5920a963b0c8434f9b288c4d8bbc8f32</t>
-  </si>
-  <si>
-    <t>感情能不能长久，就看这一点</t>
-  </si>
-  <si>
-    <t>wangcl</t>
-  </si>
-  <si>
-    <t>清新律动风</t>
-  </si>
-  <si>
-    <t>0040aa1f75cd40e78e07cc1536e3e041</t>
-  </si>
-  <si>
-    <t>「情感专一」的人，可以通过这5种表现识别</t>
-  </si>
-  <si>
-    <t>七七</t>
-  </si>
-  <si>
-    <t>0be197fa6b224e90a4295c77dc9c0e21</t>
-  </si>
-  <si>
-    <t>夫妻感情再好，永远别帮对方做这4件事，只会自讨苦吃</t>
-  </si>
-  <si>
-    <t>1471065709</t>
-  </si>
-  <si>
-    <t>cbfad670c7d44f2da94d4b575911d551</t>
-  </si>
-  <si>
-    <t>职场中，这些都是小人准备欺负你的试探信号</t>
-  </si>
-  <si>
-    <t>panyong</t>
-  </si>
-  <si>
-    <t>复古杂志风</t>
-  </si>
-  <si>
-    <t>de16bdc898c34f1d9b21752817f5cf4a</t>
-  </si>
-  <si>
-    <t>曹不见两头牛打架，让曹植作诗，不能有牛字，成千古名典</t>
-  </si>
-  <si>
-    <t>13700382410</t>
-  </si>
-  <si>
-    <t>23703d9b7a1142eeabc4392fe4e067f8</t>
-  </si>
-  <si>
-    <t>分享5个很简单的养生动作！躺着、坐着，就有惊人效果</t>
-  </si>
-  <si>
-    <t>17671924129</t>
-  </si>
-  <si>
-    <t>以下是生成规则：
-1、该sheet之前的每个sheet都是需要生成文章，在根目录下根据sheet名称创建文件夹，此文件夹作为该赛道的创作目录，根目录路径是/Users/panyong/aio_project/小程序/docs/创作目录/;
-2、创作规则：根据每个sheet里面的标题进行创作，你要根据你创作的内容生成一个120个字符以内的(包含标点符号)描述，描述要求符合SEO的原则，填写到"描述"列，如果创作完成，"是否创作完成"填写是；
-3、输出规则：输出的文件都是docx格式，并且根据每行数据的“推荐日期”列，在创作目录下创建一个输出目录，输出目录就是"创作日期"/“用户名"，文件输出到输出目录下，例如：/Users/panyong/aio_project/小程序/docs/创作目录/{date}/{用户名}/；
-4、输出文件样式：根据"样式风格"列的内容，去/Users/panyong/aio_project/小程序/services/admin-backend/styles目录下查找对应的样式文件，参考对应的样式输出文章，例如：/Users/panyong/aio_project/小程序/services/admin-backend/styles/清新律动风.docx；
-5、文件内容图片生成规则：内容中要插入图片，你可以自行下载相关图片（下载一些和标题呼应的图片，可以多找一些资源，不要总是那么几张，下载的图片必须是16:9的）；
-6、对于"是否创作完成"填写"是"的数据，就不要再重复创作了，要创作"是否创作完成"为空或者"否"的数据；</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="21">
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color indexed="8"/>
       <sz val="11"/>
-      <color indexed="8"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <color theme="1"/>
       <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
+      <color rgb="FF006100"/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <color rgb="FF9C0006"/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
+      <color rgb="FF9C6500"/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <color theme="0"/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -656,161 +483,162 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1056,7 +884,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
@@ -1065,7 +893,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
       <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
       <tableStyleElement type="headerRow" dxfId="16"/>
       <tableStyleElement type="totalRow" dxfId="15"/>
       <tableStyleElement type="firstRowStripe" dxfId="14"/>
@@ -1078,11 +906,74 @@
       <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1342,464 +1233,708 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="1" outlineLevelCol="6"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="7" width="20" customWidth="1"/>
+    <col width="20" customWidth="1" style="2" min="1" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
+    <row r="1">
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>标题名称</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="inlineStr">
+        <is>
+          <t>用户名</t>
+        </is>
+      </c>
+      <c r="D1" s="0" t="inlineStr">
+        <is>
+          <t>样式风格</t>
+        </is>
+      </c>
+      <c r="E1" s="0" t="inlineStr">
+        <is>
+          <t>描述</t>
+        </is>
+      </c>
+      <c r="F1" s="0" t="inlineStr">
+        <is>
+          <t>推荐日期</t>
+        </is>
+      </c>
+      <c r="G1" s="0" t="inlineStr">
+        <is>
+          <t>是否创作完成</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" t="s">
-        <v>11</v>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>f3fbece663d44fa1bcfc335e8741b56f</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>别再瞎发了！公众号文章怎么发，才能进入流量池？我的方法很简单</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t>taotao</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="inlineStr">
+        <is>
+          <t>基础风格</t>
+        </is>
+      </c>
+      <c r="E2" s="0" t="inlineStr">
+        <is>
+          <t>公众号文章怎么发才能进入流量池｜深度解析公众号推荐机制，揭秘标题写作、开头抓人、排版优化的3大核心方法，分享极简日更创作流，助你突破流量瓶颈，实现阅读量爆发式增长。</t>
+        </is>
+      </c>
+      <c r="F2" s="0" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G2" s="0" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="7" outlineLevelCol="6"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="7"/>
   <cols>
-    <col min="1" max="7" width="20" customWidth="1"/>
+    <col width="20" customWidth="1" style="2" min="1" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
+    <row r="1">
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>标题名称</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="inlineStr">
+        <is>
+          <t>用户名</t>
+        </is>
+      </c>
+      <c r="D1" s="0" t="inlineStr">
+        <is>
+          <t>样式风格</t>
+        </is>
+      </c>
+      <c r="E1" s="0" t="inlineStr">
+        <is>
+          <t>描述</t>
+        </is>
+      </c>
+      <c r="F1" s="0" t="inlineStr">
+        <is>
+          <t>推荐日期</t>
+        </is>
+      </c>
+      <c r="G1" s="0" t="inlineStr">
+        <is>
+          <t>是否创作完成</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" t="s">
-        <v>11</v>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>0aa7a8cbf24e4160ae6ffd55fd6d592c</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>50岁恋综：中年人的情感困境</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t>yanghm</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="inlineStr">
+        <is>
+          <t>基础风格</t>
+        </is>
+      </c>
+      <c r="E2" s="0" t="inlineStr">
+        <is>
+          <t>50岁恋综深度解析中年人的情感困境｜揭秘中年人谈爱的3大痛点：过去太重、信任太难、时间太少，探讨中年爱情的真实模样，愿你不管几岁都能勇敢去爱。</t>
+        </is>
+      </c>
+      <c r="F2" s="0" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G2" s="0" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:7">
-      <c r="A3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" t="s">
-        <v>11</v>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>41c3ce003ab04d209ec5a3e44f29d7f5</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>这个星座别在亲密关系中回避情感依赖</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t>shuxing</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t>科技蓝标签风</t>
+        </is>
+      </c>
+      <c r="E3" s="0" t="inlineStr">
+        <is>
+          <t>这个星座别在亲密关系中回避情感依赖｜深度解析回避型依恋的3个信号，教你从小事开始练习健康依赖，在独立与亲密之间找到平衡，建立更深层的情感连接。</t>
+        </is>
+      </c>
+      <c r="F3" s="0" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G3" s="0" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
     </row>
-    <row r="4" spans="1:7">
-      <c r="A4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" t="s">
-        <v>11</v>
+    <row r="4">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t>85f138d247c2405b8917649a16e0cf93</t>
+        </is>
+      </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>心理学上有个词叫：情感饥饿（我坚持不找你，不是因为不想你，更不是因为不爱你，而是因为你给我的感觉，像是我在打扰你）</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t>sumy</t>
+        </is>
+      </c>
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t>法式奶油日落风</t>
+        </is>
+      </c>
+      <c r="E4" s="0" t="inlineStr">
+        <is>
+          <t>心理学情感饥饿深度解读｜揭秘情感饥饿的3大表现：过度懂事、自我说服、情绪麻木，教你如何疗愈情感匮乏，在亲密关系中被看见、被回应、被珍惜。</t>
+        </is>
+      </c>
+      <c r="F4" s="0" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G4" s="0" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
     </row>
-    <row r="5" spans="1:7">
-      <c r="A5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" t="s">
-        <v>11</v>
+    <row r="5">
+      <c r="A5" s="0" t="inlineStr">
+        <is>
+          <t>650c156ce3a0424b874c64efe84944b8</t>
+        </is>
+      </c>
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t>心理学上说：越是分房睡、经济AA制、不干涉对方隐私的夫妻，感情浓度往往越低，越把婚姻过成</t>
+        </is>
+      </c>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t>fangwj</t>
+        </is>
+      </c>
+      <c r="D5" s="0" t="inlineStr">
+        <is>
+          <t>基础风格</t>
+        </is>
+      </c>
+      <c r="E5" s="0" t="inlineStr">
+        <is>
+          <t>心理学深度解析：分房睡、经济AA制、不干涉隐私如何降低婚姻感情浓度｜揭秘"独立婚姻"的3大隐患，教你重建婚姻浓度的方法，让婚姻回归亲密而非室友关系。</t>
+        </is>
+      </c>
+      <c r="F5" s="0" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G5" s="0" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
     </row>
-    <row r="6" spans="1:7">
-      <c r="A6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" t="s">
-        <v>11</v>
+    <row r="6">
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t>5920a963b0c8434f9b288c4d8bbc8f32</t>
+        </is>
+      </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t>感情能不能长久，就看这一点</t>
+        </is>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t>wangcl</t>
+        </is>
+      </c>
+      <c r="D6" s="0" t="inlineStr">
+        <is>
+          <t>清新律动风</t>
+        </is>
+      </c>
+      <c r="E6" s="0" t="inlineStr">
+        <is>
+          <t>感情能不能长久就看这一点｜深度解析吵架对感情的3种段位，教你从翻旧账青铜升级为沟通王者，掌握和解仪式与队友思维，让感情越吵越亲密。</t>
+        </is>
+      </c>
+      <c r="F6" s="0" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G6" s="0" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
     </row>
-    <row r="7" spans="1:7">
-      <c r="A7" t="s">
-        <v>31</v>
-      </c>
-      <c r="B7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" t="s">
-        <v>11</v>
+    <row r="7">
+      <c r="A7" s="0" t="inlineStr">
+        <is>
+          <t>0040aa1f75cd40e78e07cc1536e3e041</t>
+        </is>
+      </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t>「情感专一」的人，可以通过这5种表现识别</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t>七七</t>
+        </is>
+      </c>
+      <c r="D7" s="0" t="inlineStr">
+        <is>
+          <t>法式奶油日落风</t>
+        </is>
+      </c>
+      <c r="E7" s="0" t="inlineStr">
+        <is>
+          <t>情感专一的5种表现识别指南｜从边界感、未来规划、为你改变、情绪稳定、不说分手5个维度，教你识别真正专一的人，找到那个眼里只有你的TA。</t>
+        </is>
+      </c>
+      <c r="F7" s="0" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G7" s="0" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
     </row>
-    <row r="8" spans="1:7">
-      <c r="A8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8" t="s">
-        <v>36</v>
-      </c>
-      <c r="D8" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" t="s">
-        <v>11</v>
+    <row r="8">
+      <c r="A8" s="0" t="inlineStr">
+        <is>
+          <t>0be197fa6b224e90a4295c77dc9c0e21</t>
+        </is>
+      </c>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t>夫妻感情再好，永远别帮对方做这4件事，只会自讨苦吃</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t>1471065709</t>
+        </is>
+      </c>
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t>法式奶油日落风</t>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr">
+        <is>
+          <t>夫妻感情再好也别帮对方做这4件事｜深度解析婚姻中人际矛盾、经济压力、决策权、情绪边界4大雷区，教你建立健康边界，让关系更长久更平衡。</t>
+        </is>
+      </c>
+      <c r="F8" s="0" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G8" s="0" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="1" outlineLevelCol="6"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="7" width="20" customWidth="1"/>
+    <col width="20" customWidth="1" style="2" min="1" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
+    <row r="1">
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>标题名称</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="inlineStr">
+        <is>
+          <t>用户名</t>
+        </is>
+      </c>
+      <c r="D1" s="0" t="inlineStr">
+        <is>
+          <t>样式风格</t>
+        </is>
+      </c>
+      <c r="E1" s="0" t="inlineStr">
+        <is>
+          <t>描述</t>
+        </is>
+      </c>
+      <c r="F1" s="0" t="inlineStr">
+        <is>
+          <t>推荐日期</t>
+        </is>
+      </c>
+      <c r="G1" s="0" t="inlineStr">
+        <is>
+          <t>是否创作完成</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" t="s">
-        <v>11</v>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>cbfad670c7d44f2da94d4b575911d551</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>职场中，这些都是小人准备欺负你的试探信号</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t>panyong</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="inlineStr">
+        <is>
+          <t>复古杂志风</t>
+        </is>
+      </c>
+      <c r="E2" s="0" t="inlineStr">
+        <is>
+          <t>职场小人欺负你的试探信号识别指南｜深度解析突然热情、公开开玩笑、打听私事3大试探手段，教你设立边界、保持锋芒，保护自己不被职场小人盯上。</t>
+        </is>
+      </c>
+      <c r="F2" s="0" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G2" s="0" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="1" outlineLevelCol="6"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="7" width="20" customWidth="1"/>
+    <col width="20" customWidth="1" style="2" min="1" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
+    <row r="1">
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>标题名称</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="inlineStr">
+        <is>
+          <t>用户名</t>
+        </is>
+      </c>
+      <c r="D1" s="0" t="inlineStr">
+        <is>
+          <t>样式风格</t>
+        </is>
+      </c>
+      <c r="E1" s="0" t="inlineStr">
+        <is>
+          <t>描述</t>
+        </is>
+      </c>
+      <c r="F1" s="0" t="inlineStr">
+        <is>
+          <t>推荐日期</t>
+        </is>
+      </c>
+      <c r="G1" s="0" t="inlineStr">
+        <is>
+          <t>是否创作完成</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" t="s">
-        <v>11</v>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>de16bdc898c34f1d9b21752817f5cf4a</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>曹不见两头牛打架，让曹植作诗，不能有牛字，成千古名典</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t>13700382410</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="inlineStr">
+        <is>
+          <t>清新律动风</t>
+        </is>
+      </c>
+      <c r="E2" s="0" t="inlineStr">
+        <is>
+          <t>曹丕命曹植作诗不能有牛字却成千古名典｜深度解析"两肉齐行道"的政治隐喻，揭秘才高八斗的曹植如何在夹缝中以诗明志，赏析无字写牛的绝妙技巧。</t>
+        </is>
+      </c>
+      <c r="F2" s="0" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G2" s="0" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="1" outlineLevelCol="6"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="7" width="20" customWidth="1"/>
+    <col width="20" customWidth="1" style="2" min="1" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
+    <row r="1">
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>标题名称</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="inlineStr">
+        <is>
+          <t>用户名</t>
+        </is>
+      </c>
+      <c r="D1" s="0" t="inlineStr">
+        <is>
+          <t>样式风格</t>
+        </is>
+      </c>
+      <c r="E1" s="0" t="inlineStr">
+        <is>
+          <t>描述</t>
+        </is>
+      </c>
+      <c r="F1" s="0" t="inlineStr">
+        <is>
+          <t>推荐日期</t>
+        </is>
+      </c>
+      <c r="G1" s="0" t="inlineStr">
+        <is>
+          <t>是否创作完成</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" t="s">
-        <v>11</v>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>23703d9b7a1142eeabc4392fe4e067f8</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>分享5个很简单的养生动作！躺着、坐着，就有惊人效果</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t>17671924129</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="inlineStr">
+        <is>
+          <t>清新律动风</t>
+        </is>
+      </c>
+      <c r="E2" s="0" t="inlineStr">
+        <is>
+          <t>5个简单养生动作躺着坐着就有惊人效果｜还阳卧、搓耳朵、腹式呼吸、踮脚尖、叩齿吞津，每天不到30分钟，调理肾气、疏通经络、减压助眠、强心脏、养脾胃。</t>
+        </is>
+      </c>
+      <c r="F2" s="0" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G2" s="0" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="60" customWidth="1"/>
+    <col width="60" customWidth="1" style="2" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="404" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>47</v>
+    <row r="1" ht="404" customHeight="1" s="2">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>以下是生成规则：
+1、该sheet之前的每个sheet都是需要生成文章，在根目录下根据sheet名称创建文件夹，此文件夹作为该赛道的创作目录，根目录路径是/Users/panyong/aio_project/小程序/docs/创作目录/;
+2、创作规则：根据每个sheet里面的标题进行创作，你要根据你创作的内容生成一个120个字符以内的(包含标点符号)描述，描述要求符合SEO的原则，填写到"描述"列，如果创作完成，"是否创作完成"填写是；
+3、输出规则：输出的文件都是docx格式，并且根据每行数据的“推荐日期”列，在创作目录下创建一个输出目录，输出目录就是"创作日期"/“用户名"，文件输出到输出目录下，例如：/Users/panyong/aio_project/小程序/docs/创作目录/{date}/{用户名}/；
+4、输出文件样式：根据"样式风格"列的内容，去/Users/panyong/aio_project/小程序/services/admin-backend/styles目录下查找对应的样式文件，参考对应的样式输出文章，例如：/Users/panyong/aio_project/小程序/services/admin-backend/styles/清新律动风.docx；
+5、文件内容图片生成规则：内容中要插入图片，你可以自行下载相关图片（下载一些和标题呼应的图片，可以多找一些资源，不要总是那么几张，下载的图片必须是16:9的）；
+6、对于"是否创作完成"填写"是"的数据，就不要再重复创作了，要创作"是否创作完成"为空或者"否"的数据；</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>